--- a/docs/reports/MU.xlsx
+++ b/docs/reports/MU.xlsx
@@ -570,7 +570,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Technology · Standard (2-Stage FCFE) · generated 2026-07-08 · data: yfinance</t>
+          <t>Technology · Standard (2-Stage FCFE) · generated 2026-07-09 · data: yfinance</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2389.3092623574</v>
+        <v>34784.0660543677</v>
       </c>
     </row>
     <row r="8">
@@ -3241,34 +3241,34 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
+        <v>129585.33546</v>
+      </c>
+      <c r="C5" s="12" t="n">
         <v>234244.72475</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="D5" s="13" t="n">
         <v>241272.0664925</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="E5" s="13" t="n">
         <v>248510.228487275</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="F5" s="13" t="n">
         <v>255965.5353418932</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="G5" s="13" t="n">
         <v>263644.5014021501</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="H5" s="13" t="n">
         <v>271553.8364442146</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="I5" s="13" t="n">
         <v>279700.451537541</v>
       </c>
-      <c r="I5" s="13" t="n">
+      <c r="J5" s="13" t="n">
         <v>288091.4650836673</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="K5" s="13" t="n">
         <v>296734.2090361773</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>305636.2353072626</v>
       </c>
     </row>
     <row r="6">
@@ -3410,34 +3410,34 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
+        <v>82812.58338810234</v>
+      </c>
+      <c r="C9" s="12" t="n">
         <v>169000.6518501875</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="D9" s="13" t="n">
         <v>55118.57712503231</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="E9" s="13" t="n">
         <v>56772.13443878327</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="F9" s="13" t="n">
         <v>58475.29847194678</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="G9" s="13" t="n">
         <v>60229.55742610518</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>62036.44414888834</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>63897.53747335499</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="J9" s="13" t="n">
         <v>65814.46359755564</v>
       </c>
-      <c r="J9" s="13" t="n">
+      <c r="K9" s="13" t="n">
         <v>67788.89750548231</v>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>69822.56443064677</v>
       </c>
     </row>
     <row r="10">
@@ -3494,34 +3494,34 @@
         </is>
       </c>
       <c r="B12" s="17" t="n">
+        <v>82812.58338810234</v>
+      </c>
+      <c r="C12" s="17" t="n">
         <v>169000.6518501875</v>
       </c>
-      <c r="C12" s="17" t="n">
-        <v>174915.674664944</v>
-      </c>
       <c r="D12" s="17" t="n">
-        <v>181037.7232782171</v>
+        <v>326003.8397810436</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>187374.0435929546</v>
+        <v>592433.1486843799</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>193932.135118708</v>
+        <v>1010398.895318363</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>200719.7598478628</v>
+        <v>1610329.15217504</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>207744.951442538</v>
+        <v>2386515.342321874</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>215016.0247430268</v>
+        <v>3270131.027217511</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>222541.5856090327</v>
+        <v>4115467.552355631</v>
       </c>
       <c r="K12" s="17" t="n">
-        <v>230330.5411053488</v>
+        <v>4719417.232331335</v>
       </c>
     </row>
     <row r="13">
@@ -3720,7 +3720,7 @@
         <v>2026</v>
       </c>
       <c r="B15" s="12" t="n">
-        <v>169000.6518501875</v>
+        <v>82812.58338810234</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>2027</v>
       </c>
       <c r="B16" s="12" t="n">
-        <v>174915.674664944</v>
+        <v>169000.6518501875</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>2028</v>
       </c>
       <c r="B17" s="12" t="n">
-        <v>181037.7232782171</v>
+        <v>326003.8397810436</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>2029</v>
       </c>
       <c r="B18" s="12" t="n">
-        <v>187374.0435929546</v>
+        <v>592433.1486843799</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>2030</v>
       </c>
       <c r="B19" s="12" t="n">
-        <v>193932.135118708</v>
+        <v>1010398.895318363</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>2031</v>
       </c>
       <c r="B20" s="12" t="n">
-        <v>200719.7598478628</v>
+        <v>1610329.15217504</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>2032</v>
       </c>
       <c r="B21" s="12" t="n">
-        <v>207744.951442538</v>
+        <v>2386515.342321874</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>2033</v>
       </c>
       <c r="B22" s="12" t="n">
-        <v>215016.0247430268</v>
+        <v>3270131.027217511</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>2034</v>
       </c>
       <c r="B23" s="12" t="n">
-        <v>222541.5856090327</v>
+        <v>4115467.552355631</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>2035</v>
       </c>
       <c r="B24" s="12" t="n">
-        <v>230330.5411053488</v>
+        <v>4719417.232331335</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue cells are inputs — change them and the whole model recalculates. Source: yfinance, retrieved 2026-07-08.</t>
+          <t>Blue cells are inputs — change them and the whole model recalculates. Source: yfinance, retrieved 2026-07-09.</t>
         </is>
       </c>
     </row>

--- a/docs/reports/MU.xlsx
+++ b/docs/reports/MU.xlsx
@@ -3247,28 +3247,28 @@
         <v>234244.72475</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>241272.0664925</v>
+        <v>448303.4103446687</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>248510.228487275</v>
+        <v>801050.9487743712</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>255965.5353418932</v>
+        <v>1329644.443596859</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>263644.5014021501</v>
+        <v>2038211.967589626</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>271553.8364442146</v>
+        <v>2865573.160533444</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>279700.451537541</v>
+        <v>3664924.793664249</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>288091.4650836673</v>
+        <v>4221901.739181372</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>296734.2090361773</v>
+        <v>4327449.282660907</v>
       </c>
     </row>
     <row r="6">
@@ -3412,32 +3412,32 @@
       <c r="B9" s="12" t="n">
         <v>82812.58338810234</v>
       </c>
-      <c r="C9" s="12" t="n">
-        <v>169000.6518501875</v>
+      <c r="C9" s="13" t="n">
+        <v>52882.26007212917</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>55118.57712503231</v>
+        <v>101207.3913825426</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>56772.13443878327</v>
+        <v>180842.4272918962</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>58475.29847194678</v>
+        <v>300175.8240011362</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>60229.55742610518</v>
+        <v>460139.5206113417</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>62036.44414888834</v>
+        <v>646921.6555155005</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>63897.53747335499</v>
+        <v>827380.4513215494</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>65814.46359755564</v>
+        <v>953121.5954111418</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>67788.89750548231</v>
+        <v>976949.6352964203</v>
       </c>
     </row>
     <row r="10">
